--- a/content/tz-kursy-dlya-prepodavateley-kitayskogo-yazyka.xlsx
+++ b/content/tz-kursy-dlya-prepodavateley-kitayskogo-yazyka.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ТЗ на статью «Преподавать китайский как профи: чек-лист по выбору курсов повышения квалификации» (раздел «Преподавателям»).</t>
+          <t>ТЗ на статью «Курсы для преподавателей китайского языка: чек-лист по выбору программы» (раздел «Преподавателям»).</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Преподавать китайский как профи: чек-лист по выбору курсов повышения квалификации</t>
+          <t>Курсы для преподавателей китайского языка: чек-лист по выбору программы</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Преподавать китайский как профи: чек-лист по выбору курсов повышения квалификации</t>
+          <t>Курсы для преподавателей китайского языка: чек-лист по выбору программы</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Курсы для преподавателей китайского: чек-лист по выбору</t>
+          <t>Курсы для преподавателей китайского языка: чек-лист по выбору</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">

--- a/content/tz-kursy-dlya-prepodavateley-kitayskogo-yazyka.xlsx
+++ b/content/tz-kursy-dlya-prepodavateley-kitayskogo-yazyka.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Вписать ссылку на https://kitai-school.ru/teachers. Сделано в 6 местах: ссылка в боковой колонке (поставлена первой), кнопка в боковой колонке, две ссылки в разделе «Что мы даём», ссылка в тексте CTA, кнопка CTA.</t>
+          <t>Вписать ссылку на https://kitai-school.ru/teachers. Сделано в 6 местах: ссылка в боковой колонке (поставлена первой), кнопка в боковой колонке, две ссылки в разделе «Что мы даём», ссылка в тексте CTA, кнопка CTA. Основной анкор в тексте — «программа для преподавателей китайского языка» (раздел «Что мы даём в своей программе»).</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6 мест — требование брифа выполнено</t>
+          <t>6 мест; основной анкор — «программа для преподавателей китайского языка»</t>
         </is>
       </c>
     </row>
